--- a/artfynd/A 20087-2025 artfynd.xlsx
+++ b/artfynd/A 20087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103969114</v>
+        <v>103969112</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488786.2268660134</v>
+        <v>488766</v>
       </c>
       <c r="R2" t="n">
-        <v>6964404.033907528</v>
+        <v>6964412</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103969112</v>
+        <v>103969114</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488766.1024591054</v>
+        <v>488786</v>
       </c>
       <c r="R3" t="n">
-        <v>6964411.87744474</v>
+        <v>6964404</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,54 +907,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103969132</v>
+        <v>103969127</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skethålet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488726.220844799</v>
+        <v>488918</v>
       </c>
       <c r="R4" t="n">
-        <v>6964401.03798514</v>
+        <v>6964240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,12 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Körspår</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1048,50 +1023,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103969139</v>
+        <v>103969124</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kilån, Jmt</t>
+          <t>Skethålet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488802.6220468947</v>
+        <v>488749</v>
       </c>
       <c r="R5" t="n">
-        <v>6964376.994845612</v>
+        <v>6964390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1133,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103969110</v>
+        <v>103969141</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,34 +1150,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kilån, Jmt</t>
+          <t>Skethålet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488796.665171974</v>
+        <v>488924</v>
       </c>
       <c r="R6" t="n">
-        <v>6964376.100476411</v>
+        <v>6964199</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,15 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103969134</v>
+        <v>103969126</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488789.4124114445</v>
+        <v>488769</v>
       </c>
       <c r="R7" t="n">
-        <v>6964398.077617466</v>
+        <v>6964394</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103969152</v>
+        <v>103969134</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488907.2132223856</v>
+        <v>488789</v>
       </c>
       <c r="R8" t="n">
-        <v>6964427.404543475</v>
+        <v>6964398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,37 +1487,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103969143</v>
+        <v>103969152</v>
       </c>
       <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1572,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488904.0104944382</v>
+        <v>488907</v>
       </c>
       <c r="R9" t="n">
-        <v>6964428.330034976</v>
+        <v>6964428</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1656,12 +1606,7 @@
         <v>103969092</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,10 +1638,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488768.4048536629</v>
+        <v>488768</v>
       </c>
       <c r="R10" t="n">
-        <v>6964415.528271648</v>
+        <v>6964416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1774,15 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103969150</v>
+        <v>103969110</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,14 +1750,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skethålet, Jmt</t>
+          <t>Kilån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488899.8949123542</v>
+        <v>488797</v>
       </c>
       <c r="R11" t="n">
-        <v>6964430.173285662</v>
+        <v>6964376</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1789,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1799,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,15 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103969126</v>
+        <v>103969150</v>
       </c>
       <c r="B12" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,21 +1846,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1935,10 +1870,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488768.3297738274</v>
+        <v>488900</v>
       </c>
       <c r="R12" t="n">
-        <v>6964393.576253594</v>
+        <v>6964430</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,7 +1905,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,7 +1915,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,37 +1951,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103969124</v>
+        <v>103969143</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2056,10 +1986,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488749.5385418293</v>
+        <v>488904</v>
       </c>
       <c r="R13" t="n">
-        <v>6964389.524508758</v>
+        <v>6964429</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2091,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2101,7 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2137,50 +2067,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103969141</v>
+        <v>103969139</v>
       </c>
       <c r="B14" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skethålet, Jmt</t>
+          <t>Kilån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488923.8450144478</v>
+        <v>488803</v>
       </c>
       <c r="R14" t="n">
-        <v>6964198.672602098</v>
+        <v>6964377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2212,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2222,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2251,6 +2176,132 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>103969132</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skethålet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488726</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6964401</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-06-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Körspår</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 20087-2025 artfynd.xlsx
+++ b/artfynd/A 20087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969112</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969114</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969124</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969141</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969126</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969134</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969152</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969092</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969110</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969150</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969143</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2178,6 +2243,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969139</t>
         </is>
       </c>
     </row>
@@ -2306,8 +2376,29 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103969132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>